--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:20:22+00:00</t>
+    <t>2025-01-06T16:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:22:16+00:00</t>
+    <t>2025-01-14T14:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T14:51:40+00:00</t>
+    <t>2025-01-14T21:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T21:51:01+00:00</t>
+    <t>2025-01-15T14:08:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="140">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-15T14:08:36+00:00</t>
+    <t>2025-01-17T15:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,6 +311,10 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
+</t>
   </si>
   <si>
     <t>AuthoringDevice.typeId.nullFlavor</t>
@@ -1295,7 +1299,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1303,10 +1307,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1404,17 +1408,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -1432,11 +1436,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1487,7 +1491,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1507,17 +1511,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1535,11 +1539,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1590,7 +1594,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1610,17 +1614,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1638,11 +1642,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1651,7 +1655,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -1693,7 +1697,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1713,17 +1717,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1741,11 +1745,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1796,7 +1800,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1816,10 +1820,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1846,7 +1850,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1897,7 +1901,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -1917,10 +1921,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1954,7 +1958,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -1976,7 +1980,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -1994,7 +1998,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2014,10 +2018,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2051,7 +2055,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2073,7 +2077,7 @@
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2091,7 +2095,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2111,10 +2115,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2137,7 +2141,7 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -2166,11 +2170,11 @@
         <v>74</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>74</v>
@@ -2188,7 +2192,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2208,10 +2212,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2234,7 +2238,7 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -2263,11 +2267,11 @@
         <v>74</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>74</v>
@@ -2285,7 +2289,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2305,10 +2309,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2331,7 +2335,7 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -2360,29 +2364,29 @@
         <v>74</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>136</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>135</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2402,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2428,7 +2432,7 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -2481,7 +2485,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:05:21+00:00</t>
+    <t>2025-02-03T10:34:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="142">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T10:34:19+00:00</t>
+    <t>2025-02-05T14:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -430,10 +430,16 @@
 </t>
   </si>
   <si>
+    <t>Nom du modèle du système.</t>
+  </si>
+  <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ManufacturerModelNameExample</t>
   </si>
   <si>
     <t>AuthoringDevice.softwareName</t>
+  </si>
+  <si>
+    <t>Nom du système.</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-SoftwareNameExample</t>
@@ -2240,7 +2246,9 @@
       <c r="K15" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L15" s="2"/>
+      <c r="L15" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2271,7 +2279,7 @@
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>74</v>
@@ -2309,10 +2317,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2337,7 +2345,9 @@
       <c r="K16" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L16" s="2"/>
+      <c r="L16" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2368,25 +2378,25 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2406,10 +2416,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2432,7 +2442,7 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -2485,7 +2495,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:18:33+00:00</t>
+    <t>2025-02-05T15:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:17:43+00:00</t>
+    <t>2025-02-05T15:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:35:39+00:00</t>
+    <t>2025-02-06T13:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>authoringDevice contient les informations complémentaires si l’auteur est un système.</t>
+    <t>L'élément de l'en-tête du CDA authoringDevice contient les informations complémentaires si l’auteur est un système.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-authoring-device.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-authoring-device.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T13:21:10+00:00</t>
+    <t>2025-02-06T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
